--- a/outputs/q4/inventory_trace.xlsx
+++ b/outputs/q4/inventory_trace.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>生产需求产品当量</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>预测可供货量</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>计划发运量</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>周转运总能力</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>实际到厂产品当量</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>实际库存产品当量</t>
         </is>
@@ -450,10 +470,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>52322.10926407322</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C2" t="n">
-        <v>102294.2731529621</v>
+        <v>26003.07235849819</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26003.07235849818</v>
+      </c>
+      <c r="E2" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39872.53215135064</v>
+      </c>
+      <c r="G2" t="n">
+        <v>75526.49221605904</v>
       </c>
     </row>
     <row r="3">
@@ -461,10 +493,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C3" t="n">
-        <v>104644.2185281465</v>
+        <v>23344.09234378129</v>
+      </c>
+      <c r="D3" t="n">
+        <v>23344.09234378129</v>
+      </c>
+      <c r="E3" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>35622.89284904267</v>
+      </c>
+      <c r="G3" t="n">
+        <v>75495.42500039333</v>
       </c>
     </row>
     <row r="4">
@@ -472,10 +516,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C4" t="n">
-        <v>106994.1639033308</v>
+        <v>24895.8804881235</v>
+      </c>
+      <c r="D4" t="n">
+        <v>24895.8804881235</v>
+      </c>
+      <c r="E4" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>37906.83127465905</v>
+      </c>
+      <c r="G4" t="n">
+        <v>77748.29621034399</v>
       </c>
     </row>
     <row r="5">
@@ -483,10 +539,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C5" t="n">
-        <v>109344.1092785152</v>
+        <v>23797.67242043015</v>
+      </c>
+      <c r="D5" t="n">
+        <v>23797.67242043015</v>
+      </c>
+      <c r="E5" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>36254.35602345037</v>
+      </c>
+      <c r="G5" t="n">
+        <v>78348.69216908599</v>
       </c>
     </row>
     <row r="6">
@@ -494,10 +562,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C6" t="n">
-        <v>111694.0546536995</v>
+        <v>24715.61236743693</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24537.81236743692</v>
+      </c>
+      <c r="E6" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>37435.68661970771</v>
+      </c>
+      <c r="G6" t="n">
+        <v>80130.41872408532</v>
       </c>
     </row>
     <row r="7">
@@ -505,10 +585,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C7" t="n">
-        <v>114044.0000288839</v>
+        <v>25124.56242565929</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25081.93771862088</v>
+      </c>
+      <c r="E7" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F7" t="n">
+        <v>38242.68351871493</v>
+      </c>
+      <c r="G7" t="n">
+        <v>82719.14217809186</v>
       </c>
     </row>
     <row r="8">
@@ -516,10 +608,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C8" t="n">
-        <v>116393.9454040682</v>
+        <v>24380.0172290487</v>
+      </c>
+      <c r="D8" t="n">
+        <v>24341.5422290487</v>
+      </c>
+      <c r="E8" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F8" t="n">
+        <v>37173.29575024852</v>
+      </c>
+      <c r="G8" t="n">
+        <v>84238.477863632</v>
       </c>
     </row>
     <row r="9">
@@ -527,10 +631,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C9" t="n">
-        <v>118743.8907792526</v>
+        <v>24130.79513166729</v>
+      </c>
+      <c r="D9" t="n">
+        <v>24092.32013166729</v>
+      </c>
+      <c r="E9" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F9" t="n">
+        <v>36791.98738690661</v>
+      </c>
+      <c r="G9" t="n">
+        <v>85376.50518583022</v>
       </c>
     </row>
     <row r="10">
@@ -538,10 +654,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C10" t="n">
-        <v>121093.8361544369</v>
+        <v>25536.67628404784</v>
+      </c>
+      <c r="D10" t="n">
+        <v>24498.16423032635</v>
+      </c>
+      <c r="E10" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F10" t="n">
+        <v>37411.04197833413</v>
+      </c>
+      <c r="G10" t="n">
+        <v>87133.58709945597</v>
       </c>
     </row>
     <row r="11">
@@ -549,10 +677,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C11" t="n">
-        <v>123443.7815296213</v>
+        <v>25858.75177106938</v>
+      </c>
+      <c r="D11" t="n">
+        <v>24560.6328631399</v>
+      </c>
+      <c r="E11" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F11" t="n">
+        <v>37411.49563947431</v>
+      </c>
+      <c r="G11" t="n">
+        <v>88891.12267422189</v>
       </c>
     </row>
     <row r="12">
@@ -560,10 +700,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C12" t="n">
-        <v>125793.7269048056</v>
+        <v>26448.43776040862</v>
+      </c>
+      <c r="D12" t="n">
+        <v>24555.43612456682</v>
+      </c>
+      <c r="E12" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F12" t="n">
+        <v>37411.17102677746</v>
+      </c>
+      <c r="G12" t="n">
+        <v>90648.33363629096</v>
       </c>
     </row>
     <row r="13">
@@ -571,10 +723,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C13" t="n">
-        <v>128143.67227999</v>
+        <v>25987.26490623591</v>
+      </c>
+      <c r="D13" t="n">
+        <v>24548.90870724275</v>
+      </c>
+      <c r="E13" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F13" t="n">
+        <v>37411.24093263457</v>
+      </c>
+      <c r="G13" t="n">
+        <v>92405.61450421714</v>
       </c>
     </row>
     <row r="14">
@@ -582,10 +746,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C14" t="n">
-        <v>130493.6176551744</v>
+        <v>26523.35693681151</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24483.27058049538</v>
+      </c>
+      <c r="E14" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F14" t="n">
+        <v>37411.66638707968</v>
+      </c>
+      <c r="G14" t="n">
+        <v>94163.32082658843</v>
       </c>
     </row>
     <row r="15">
@@ -593,10 +769,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C15" t="n">
-        <v>132843.5630303587</v>
+        <v>27347.65691565125</v>
+      </c>
+      <c r="D15" t="n">
+        <v>24530.77250725676</v>
+      </c>
+      <c r="E15" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F15" t="n">
+        <v>37410.90242251738</v>
+      </c>
+      <c r="G15" t="n">
+        <v>95920.26318439742</v>
       </c>
     </row>
     <row r="16">
@@ -604,10 +792,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C16" t="n">
-        <v>135193.508405543</v>
+        <v>26576.19924408672</v>
+      </c>
+      <c r="D16" t="n">
+        <v>24543.39324541569</v>
+      </c>
+      <c r="E16" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F16" t="n">
+        <v>37410.86523297767</v>
+      </c>
+      <c r="G16" t="n">
+        <v>97677.1683526667</v>
       </c>
     </row>
     <row r="17">
@@ -615,10 +815,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C17" t="n">
-        <v>137543.4537807274</v>
+        <v>25596.77568109139</v>
+      </c>
+      <c r="D17" t="n">
+        <v>24563.92571460397</v>
+      </c>
+      <c r="E17" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F17" t="n">
+        <v>37410.79633443801</v>
+      </c>
+      <c r="G17" t="n">
+        <v>99434.00462239633</v>
       </c>
     </row>
     <row r="18">
@@ -626,10 +838,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C18" t="n">
-        <v>139893.3991559118</v>
+        <v>25790.63040936093</v>
+      </c>
+      <c r="D18" t="n">
+        <v>24493.40280151369</v>
+      </c>
+      <c r="E18" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F18" t="n">
+        <v>37410.11757966598</v>
+      </c>
+      <c r="G18" t="n">
+        <v>101190.1621373539</v>
       </c>
     </row>
     <row r="19">
@@ -637,10 +861,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C19" t="n">
-        <v>142243.3445310961</v>
+        <v>27322.81815149633</v>
+      </c>
+      <c r="D19" t="n">
+        <v>24372.63095971775</v>
+      </c>
+      <c r="E19" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F19" t="n">
+        <v>37404.34349692913</v>
+      </c>
+      <c r="G19" t="n">
+        <v>102940.5455695747</v>
       </c>
     </row>
     <row r="20">
@@ -648,10 +884,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C20" t="n">
-        <v>144593.2899062805</v>
+        <v>26698.80031467488</v>
+      </c>
+      <c r="D20" t="n">
+        <v>24437.66250327436</v>
+      </c>
+      <c r="E20" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F20" t="n">
+        <v>37412.00399376058</v>
+      </c>
+      <c r="G20" t="n">
+        <v>104698.5894986269</v>
       </c>
     </row>
     <row r="21">
@@ -659,10 +907,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C21" t="n">
-        <v>146943.2352814648</v>
+        <v>25262.85161118294</v>
+      </c>
+      <c r="D21" t="n">
+        <v>24474.07752281322</v>
+      </c>
+      <c r="E21" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F21" t="n">
+        <v>37410.75707721822</v>
+      </c>
+      <c r="G21" t="n">
+        <v>106455.3865111367</v>
       </c>
     </row>
     <row r="22">
@@ -670,10 +930,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C22" t="n">
-        <v>149293.1806566492</v>
+        <v>26864.51998322848</v>
+      </c>
+      <c r="D22" t="n">
+        <v>24469.84070524525</v>
+      </c>
+      <c r="E22" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F22" t="n">
+        <v>37411.56453459854</v>
+      </c>
+      <c r="G22" t="n">
+        <v>108212.9909810268</v>
       </c>
     </row>
     <row r="23">
@@ -681,10 +953,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C23" t="n">
-        <v>151643.1260318335</v>
+        <v>26152.6598861328</v>
+      </c>
+      <c r="D23" t="n">
+        <v>24516.63686352977</v>
+      </c>
+      <c r="E23" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F23" t="n">
+        <v>37411.65174943744</v>
+      </c>
+      <c r="G23" t="n">
+        <v>109970.6826657559</v>
       </c>
     </row>
     <row r="24">
@@ -692,10 +976,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C24" t="n">
-        <v>153993.0714070179</v>
+        <v>25471.23849386234</v>
+      </c>
+      <c r="D24" t="n">
+        <v>24459.6199067374</v>
+      </c>
+      <c r="E24" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F24" t="n">
+        <v>37410.56929872667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>111727.2918997742</v>
       </c>
     </row>
     <row r="25">
@@ -703,10 +999,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>52322.10926407324</v>
+        <v>35653.96006470839</v>
       </c>
       <c r="C25" t="n">
-        <v>156343.0167822022</v>
+        <v>25203.56368599815</v>
+      </c>
+      <c r="D25" t="n">
+        <v>24482.83466070494</v>
+      </c>
+      <c r="E25" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F25" t="n">
+        <v>37411.99347918024</v>
+      </c>
+      <c r="G25" t="n">
+        <v>113485.325314246</v>
       </c>
     </row>
   </sheetData>
